--- a/knowledge_base/source/10_metadata.xlsx
+++ b/knowledge_base/source/10_metadata.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_metadata" sheetId="1" r:id="Rd2b7bc0f682c4117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_metadata" sheetId="1" r:id="Rf99cb56154c94f01"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -594,11 +594,11 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F6" s="32" t="str">
-        <x:v>Exam only; Exam and TP-153; TP-153; Generated report; All analyses</x:v>
+        <x:v>Exam evidence only; Exam and TP-153; TP-153 evidence only; Generated report output; Entire analysis</x:v>
       </x:c>
       <x:c r="G6" s="32" t="str"/>
       <x:c r="H6" s="38" t="str">
-        <x:v>Defines required inputs.</x:v>
+        <x:v>Identifies the evidence source or analysis output used by the requirement. All analyses require both the Exam PDF and populated TP-153.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
@@ -1772,7 +1772,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2e3b11c65dd4b12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R596db42d2fd3490c"/>
   </x:tableParts>
 </x:worksheet>
 </file>